--- a/borchestra_achivments_secret.xlsx
+++ b/borchestra_achivments_secret.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,24 +431,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>EP_Mastery_ACH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>null</t>
+          <t>Achieve every Non-Abstraction achievement in the Enemy Pack.</t>
         </is>
       </c>
     </row>
